--- a/Result/profitability/2431.xlsx
+++ b/Result/profitability/2431.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.34875</v>
+        <v>-0.345</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.97125</v>
+        <v>-15.94125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.35125</v>
+        <v>-0.3475</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.9275</v>
+        <v>-14.98375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.35125</v>
+        <v>-0.3525</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.01125</v>
+        <v>-14.67375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.36625</v>
+        <v>-0.35625</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.345</v>
+        <v>-13.64625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.29875</v>
+        <v>-0.28875</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.6675</v>
+        <v>-10.9</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2125</v>
+        <v>-0.02874999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.4175</v>
+        <v>5.992499999999998</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05250000000000003</v>
+        <v>0.06250000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>7.417499999999999</v>
+        <v>8.786249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.59</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1512500000000001</v>
+        <v>0.15125</v>
       </c>
       <c r="N9" t="n">
         <v>9.779999999999998</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>59</v>
+      </c>
+      <c r="D75" t="n">
+        <v>56</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-35.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-16.98625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.716300940438872</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-5.480392156862745</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
